--- a/ig/document/StructureDefinition-medcom-document-careteam.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-careteam.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:37:57+00:00</t>
+    <t>2026-03-10T10:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1620,7 +1620,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>83</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" hidden="true">
+    <row r="7">
       <c r="A7" t="s" s="2">
         <v>112</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
         <v>145</v>
       </c>
@@ -2948,7 +2948,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>167</v>
       </c>
@@ -3507,7 +3507,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
         <v>196</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
         <v>205</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>244</v>
       </c>
@@ -5721,7 +5721,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>313</v>
       </c>
@@ -6054,12 +6054,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AM42">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/document/StructureDefinition-medcom-document-careteam.xlsx
+++ b/ig/document/StructureDefinition-medcom-document-careteam.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T10:54:08+00:00</t>
+    <t>2026-04-29T08:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
